--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92295</v>
+        <v>92298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>92295</v>
+        <v>92298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>136397162</v>
       </c>
       <c r="B4" t="n">
-        <v>92295</v>
+        <v>92298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>136397162</v>
       </c>
       <c r="B4" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92299</v>
+        <v>92304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>92299</v>
+        <v>92304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>136397162</v>
       </c>
       <c r="B4" t="n">
-        <v>92299</v>
+        <v>92304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>136397157</v>
       </c>
       <c r="B5" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136397158</v>
       </c>
       <c r="B6" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136397161</v>
       </c>
       <c r="B7" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136365997</v>
       </c>
       <c r="B8" t="n">
-        <v>58843</v>
+        <v>58845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136397156</v>
       </c>
       <c r="B9" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136397155</v>
       </c>
       <c r="B10" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92304</v>
+        <v>92306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>92304</v>
+        <v>92306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>136397162</v>
       </c>
       <c r="B4" t="n">
-        <v>92304</v>
+        <v>92306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>136397162</v>
       </c>
       <c r="B4" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>136397157</v>
       </c>
       <c r="B5" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136397158</v>
       </c>
       <c r="B6" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136397161</v>
       </c>
       <c r="B7" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136397156</v>
       </c>
       <c r="B9" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136397155</v>
       </c>
       <c r="B10" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>136397162</v>
       </c>
       <c r="B4" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>136397157</v>
       </c>
       <c r="B5" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136397158</v>
       </c>
       <c r="B6" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136397161</v>
       </c>
       <c r="B7" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136397156</v>
       </c>
       <c r="B9" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136397155</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>136397162</v>
       </c>
       <c r="B4" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>136397157</v>
       </c>
       <c r="B5" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136397158</v>
       </c>
       <c r="B6" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136397161</v>
       </c>
       <c r="B7" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136397156</v>
       </c>
       <c r="B9" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136397155</v>
       </c>
       <c r="B10" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>136397162</v>
       </c>
       <c r="B4" t="n">
-        <v>92311</v>
+        <v>92317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
